--- a/raw_data/2026-03-27_proofread-dna-polymerases.xlsx
+++ b/raw_data/2026-03-27_proofread-dna-polymerases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\8_tak\50_my_quarto_book2_2026-03-02\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879BC37F-B13E-4D53-89B3-EE67ABB940C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE4F97B-6FAE-4FA6-81E3-5E694EC8C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
   <si>
     <t>proofread-dna-polymerase</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -123,6 +123,222 @@
   </si>
   <si>
     <t>Canace Plus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VeraSeq 2.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QIAGEN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P7511L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.qiagen.com/us/products/discovery-and-translational-research/enzymes-for-molecular-biology/veraseq-2-0-high-fidelity-dna-polymerase?catno=P7511L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HyperFusion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APExBIO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1032</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.apexbt.com/hyperfusiontm-high-fidelity-dna-polymerase.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Platinum SuperFi II</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThermoFisher</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.thermofisher.com/order/catalog/product/12361010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Platinum SuperFi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.thermofisher.com/order/catalog/product/12351010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperNova HTS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.gene-star.com/product_view.php?id=702</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>康润</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A169</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pfx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>康为世纪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CW2965S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.cwbiosciences.com/home/Products/PCR,%20qPCR,%20RT-PCR/PCR/CW2965?id=9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金沙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF213</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.genesand.com/page68?_l=zh_CN&amp;product_id=103</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾德莱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC5701</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.aidlab.cn/products-show.asp?anclassid=87&amp;nclassid=76&amp;id=1871</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloria Nova HS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱博泰克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RK20731</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://abclonal.com.cn/catalog/RK20731</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S705 HiFi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>愚公</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EG24110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.best-enzymes.com/cms/gaobaozhenDNAjuhemeiPCRMix/273.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KAPA HiFi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>07958927001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Roche</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rochesequencingstore.com/catalog/kapa-hifi-hotstart-readymix/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>provider_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NWZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QSJ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KWSJ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABTK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domestic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yes</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -485,18 +701,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.53125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.06640625" customWidth="1"/>
+    <col min="6" max="6" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -507,16 +724,22 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -527,16 +750,22 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H2" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -547,16 +776,22 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H3" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -567,16 +802,22 @@
         <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="5">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H4" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -587,16 +828,22 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H5" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -607,23 +854,326 @@
         <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="5">
+      <c r="H6" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3">
+        <v>300</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12361010</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3">
+        <v>300</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12351010</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3">
+        <v>50</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3">
+        <v>120</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="3">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="5">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="5">
         <v>46108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{78E8C416-2382-44C2-AF71-15409C9C8087}"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://www.toyobo-global.com/products/lifescience/products/pcr_001/index.html/" xr:uid="{7B0CAF43-391B-437A-994A-3D6351CB89C2}"/>
-    <hyperlink ref="E5" r:id="rId3" xr:uid="{08538B6F-152C-42FE-AAEA-107EA6C3E729}"/>
-    <hyperlink ref="E6" r:id="rId4" xr:uid="{D3B140C1-1867-4E08-A9FA-98C7689FFFC5}"/>
-    <hyperlink ref="E4" r:id="rId5" xr:uid="{93E15686-BA0C-4D09-83B2-D228B4054E10}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{78E8C416-2382-44C2-AF71-15409C9C8087}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.toyobo-global.com/products/lifescience/products/pcr_001/index.html/" xr:uid="{7B0CAF43-391B-437A-994A-3D6351CB89C2}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{08538B6F-152C-42FE-AAEA-107EA6C3E729}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{D3B140C1-1867-4E08-A9FA-98C7689FFFC5}"/>
+    <hyperlink ref="G4" r:id="rId5" xr:uid="{93E15686-BA0C-4D09-83B2-D228B4054E10}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{9B6EE3F6-2599-4128-AED1-9212CF7C2B6F}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{B8FBC6E3-9877-44DC-8A76-CDA937A9831B}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{A9CC8243-E627-49B1-A9DF-D19ABCE87F71}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{14BF584B-4D8F-414D-92AA-508BE64956E0}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{D1DE6759-17BE-453C-8D29-427436C80E77}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{1AB0BA86-5ECB-49F0-B1B2-011D2BDD5CAB}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{3477A1F1-EC36-4193-981B-3AA5F24FCB10}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{B590FA23-7C33-4F3C-ABB0-414C41A9E232}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{B2F00DB7-85A2-4A1D-847C-67D74DFB9544}"/>
+    <hyperlink ref="G16" r:id="rId15" xr:uid="{A5A705E1-2FA1-4250-B4C4-E7BF7565B191}"/>
+    <hyperlink ref="G17" r:id="rId16" xr:uid="{F8BDBB85-9C91-4820-8CE8-0709974201CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
